--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ67"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7733,10 +7733,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130840942</v>
+        <v>136935811</v>
       </c>
       <c r="B66" t="n">
-        <v>99035</v>
+        <v>58164</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7744,38 +7744,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219790</v>
+        <v>103023</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kungsudden, Dlr</t>
+          <t>Kärrgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521614</v>
+        <v>520945</v>
       </c>
       <c r="R66" t="n">
-        <v>6671827</v>
+        <v>6671076</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7802,12 +7798,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7822,27 +7818,27 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130840942</t>
+          <t>https://artportalen.se/Sighting/136935811</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130840943</v>
+        <v>136935818</v>
       </c>
       <c r="B67" t="n">
-        <v>99035</v>
+        <v>8452</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7850,38 +7846,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219790</v>
+        <v>106554</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kungsudden, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521608</v>
+        <v>521233</v>
       </c>
       <c r="R67" t="n">
-        <v>6671848</v>
+        <v>6671082</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7908,12 +7900,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7928,18 +7920,1274 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136935818</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>130840942</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Kungsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>521614</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6671827</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130840942</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>130840943</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Kungsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>521608</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6671848</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/130840943</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>136935810</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kärrgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>520944</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6671079</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136935810</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>136935812</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Kärrgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>520964</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6671093</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136935812</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>136935819</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Kungsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>521241</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6671214</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136935819</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>136935820</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Kungsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>521103</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6671163</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136935820</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>136935821</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Kungsudden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>521018</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6671217</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136935821</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>136935815</v>
+      </c>
+      <c r="B75" t="n">
+        <v>98221</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Kärrgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>521005</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6671084</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136935815</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>136935813</v>
+      </c>
+      <c r="B76" t="n">
+        <v>98215</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Kärrgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>520996</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6671087</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136935813</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>136935814</v>
+      </c>
+      <c r="B77" t="n">
+        <v>98218</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kärrgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>520998</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6671081</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136935814</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>136935816</v>
+      </c>
+      <c r="B78" t="n">
+        <v>98218</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kärrgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>521015</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6671040</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136935816</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>136935817</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98218</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Kärrgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>521142</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6671069</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Norrbärke</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136935817</t>
         </is>
       </c>
     </row>
@@ -8011,6 +9259,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98218</v>
+        <v>98224</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98218</v>
+        <v>98224</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98218</v>
+        <v>98224</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98226</v>
+        <v>98227</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98226</v>
+        <v>98227</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98226</v>
+        <v>98227</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98227</v>
+        <v>98233</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98227</v>
+        <v>98233</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98227</v>
+        <v>98233</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98233</v>
+        <v>98237</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98233</v>
+        <v>98237</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98233</v>
+        <v>98237</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98237</v>
+        <v>98239</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98237</v>
+        <v>98239</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98237</v>
+        <v>98239</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98239</v>
+        <v>98241</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98239</v>
+        <v>98241</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98239</v>
+        <v>98241</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -7736,7 +7736,7 @@
         <v>136935811</v>
       </c>
       <c r="B66" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98241</v>
+        <v>98254</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98241</v>
+        <v>98254</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98241</v>
+        <v>98254</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -7736,7 +7736,7 @@
         <v>136935811</v>
       </c>
       <c r="B66" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>136935818</v>
       </c>
       <c r="B67" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98254</v>
+        <v>98256</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98254</v>
+        <v>98256</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98254</v>
+        <v>98256</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98256</v>
+        <v>98259</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98256</v>
+        <v>98259</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98256</v>
+        <v>98259</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -7736,7 +7736,7 @@
         <v>136935811</v>
       </c>
       <c r="B66" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>136935818</v>
       </c>
       <c r="B67" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98259</v>
+        <v>98269</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98259</v>
+        <v>98269</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98259</v>
+        <v>98269</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98269</v>
+        <v>98270</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98269</v>
+        <v>98270</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98269</v>
+        <v>98270</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -7736,7 +7736,7 @@
         <v>136935811</v>
       </c>
       <c r="B66" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98270</v>
+        <v>98275</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98270</v>
+        <v>98275</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98270</v>
+        <v>98275</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98275</v>
+        <v>98277</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98275</v>
+        <v>98277</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98275</v>
+        <v>98277</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -7736,7 +7736,7 @@
         <v>136935811</v>
       </c>
       <c r="B66" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98277</v>
+        <v>98283</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98277</v>
+        <v>98283</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98277</v>
+        <v>98283</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98283</v>
+        <v>98295</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98283</v>
+        <v>98295</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98283</v>
+        <v>98295</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98295</v>
+        <v>98296</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98295</v>
+        <v>98296</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98295</v>
+        <v>98296</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98296</v>
+        <v>98299</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98296</v>
+        <v>98299</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98296</v>
+        <v>98299</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98302</v>
+        <v>98303</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98296</v>
+        <v>98297</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98299</v>
+        <v>98300</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98299</v>
+        <v>98300</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98299</v>
+        <v>98300</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/S 930-2023 artfynd.xlsx
+++ b/artfynd/S 930-2023 artfynd.xlsx
@@ -7736,7 +7736,7 @@
         <v>136935811</v>
       </c>
       <c r="B66" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>136935810</v>
       </c>
       <c r="B70" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>136935812</v>
       </c>
       <c r="B71" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>136935819</v>
       </c>
       <c r="B72" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>136935820</v>
       </c>
       <c r="B73" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136935821</v>
       </c>
       <c r="B74" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>136935815</v>
       </c>
       <c r="B75" t="n">
-        <v>98303</v>
+        <v>98306</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>136935813</v>
       </c>
       <c r="B76" t="n">
-        <v>98297</v>
+        <v>98300</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>136935814</v>
       </c>
       <c r="B77" t="n">
-        <v>98300</v>
+        <v>98303</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>136935816</v>
       </c>
       <c r="B78" t="n">
-        <v>98300</v>
+        <v>98303</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>136935817</v>
       </c>
       <c r="B79" t="n">
-        <v>98300</v>
+        <v>98303</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
